--- a/fixtures/xlsx/number-formats/input.xlsx
+++ b/fixtures/xlsx/number-formats/input.xlsx
@@ -10,16 +10,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>Value</t>
+    <t>Time</t>
   </si>
   <si>
     <t>Label</t>
   </si>
   <si>
-    <t>Currency</t>
+    <t>Value</t>
   </si>
   <si>
     <t>Percentage</t>
+  </si>
+  <si>
+    <t>PlainNumber</t>
   </si>
   <si>
     <t>Date</t>
@@ -28,10 +31,7 @@
     <t>DateTime</t>
   </si>
   <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>PlainNumber</t>
+    <t>Currency</t>
   </si>
 </sst>
 </file>
@@ -40,10 +40,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="0.00%"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="m/d/yy h:mm"/>
     <numFmt numFmtId="167" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="m/d/yy h:mm"/>
+    <numFmt numFmtId="168" formatCode="hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -93,20 +93,20 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>0.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4">
         <v>19.99</v>
@@ -114,7 +114,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
         <v>45000</v>
@@ -122,23 +122,23 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="5">
         <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>45000.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>42</v>
